--- a/data/availability/projects/marakez/crescent-walk.xlsx
+++ b/data/availability/projects/marakez/crescent-walk.xlsx
@@ -554,7 +554,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -604,7 +604,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -704,7 +704,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -754,7 +754,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1259,7 +1259,6 @@
       <c r="G2" t="n">
         <v>177</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -1292,7 +1291,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1316,7 +1315,6 @@
       <c r="G3" t="n">
         <v>179</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -1349,7 +1347,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1373,7 +1371,6 @@
       <c r="G4" t="n">
         <v>74</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -1406,7 +1403,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1430,7 +1427,6 @@
       <c r="G5" t="n">
         <v>177</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -1463,7 +1459,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1487,7 +1483,6 @@
       <c r="G6" t="n">
         <v>177</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -1544,7 +1539,6 @@
       <c r="G7" t="n">
         <v>241</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -1601,7 +1595,6 @@
       <c r="G8" t="n">
         <v>244</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -1658,7 +1651,6 @@
       <c r="G9" t="n">
         <v>241</v>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -1691,7 +1683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1752,7 +1744,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1813,7 +1805,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1837,7 +1829,6 @@
       <c r="G12" t="n">
         <v>169</v>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -1894,7 +1885,6 @@
       <c r="G13" t="n">
         <v>279</v>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -1951,7 +1941,6 @@
       <c r="G14" t="n">
         <v>313</v>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -2008,7 +1997,6 @@
       <c r="G15" t="n">
         <v>372</v>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -2065,7 +2053,6 @@
       <c r="G16" t="n">
         <v>313</v>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -2122,7 +2109,6 @@
       <c r="G17" t="n">
         <v>372</v>
       </c>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -2179,7 +2165,6 @@
       <c r="G18" t="n">
         <v>313</v>
       </c>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -2236,7 +2221,6 @@
       <c r="G19" t="n">
         <v>313</v>
       </c>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -2293,7 +2277,6 @@
       <c r="G20" t="n">
         <v>372</v>
       </c>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -2350,7 +2333,6 @@
       <c r="G21" t="n">
         <v>372</v>
       </c>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -2407,7 +2389,6 @@
       <c r="G22" t="n">
         <v>313</v>
       </c>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -2464,7 +2445,6 @@
       <c r="G23" t="n">
         <v>279</v>
       </c>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -2521,7 +2501,6 @@
       <c r="G24" t="n">
         <v>313</v>
       </c>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -2578,7 +2557,6 @@
       <c r="G25" t="n">
         <v>279</v>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -2635,7 +2613,6 @@
       <c r="G26" t="n">
         <v>372</v>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -2668,7 +2645,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2692,7 +2669,6 @@
       <c r="G27" t="n">
         <v>139</v>
       </c>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -2725,7 +2701,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2749,7 +2725,6 @@
       <c r="G28" t="n">
         <v>127</v>
       </c>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -2782,7 +2757,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2806,7 +2781,6 @@
       <c r="G29" t="n">
         <v>181</v>
       </c>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -2839,7 +2813,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2863,7 +2837,6 @@
       <c r="G30" t="n">
         <v>77</v>
       </c>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -2896,7 +2869,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2920,7 +2893,6 @@
       <c r="G31" t="n">
         <v>77</v>
       </c>
-      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -2953,7 +2925,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2977,7 +2949,6 @@
       <c r="G32" t="n">
         <v>139</v>
       </c>
-      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -3010,7 +2981,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3034,7 +3005,6 @@
       <c r="G33" t="n">
         <v>77</v>
       </c>
-      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -3067,7 +3037,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3091,7 +3061,6 @@
       <c r="G34" t="n">
         <v>139</v>
       </c>
-      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -3124,7 +3093,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3148,7 +3117,6 @@
       <c r="G35" t="n">
         <v>172</v>
       </c>
-      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -3181,7 +3149,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3242,7 +3210,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3266,7 +3234,6 @@
       <c r="G37" t="n">
         <v>177</v>
       </c>
-      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -3299,7 +3266,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3323,7 +3290,6 @@
       <c r="G38" t="n">
         <v>142</v>
       </c>
-      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -3356,7 +3322,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3380,7 +3346,6 @@
       <c r="G39" t="n">
         <v>149</v>
       </c>
-      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -3413,7 +3378,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3437,7 +3402,6 @@
       <c r="G40" t="n">
         <v>74</v>
       </c>
-      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -3470,7 +3434,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3494,7 +3458,6 @@
       <c r="G41" t="n">
         <v>142</v>
       </c>
-      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -3527,7 +3490,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3551,7 +3514,6 @@
       <c r="G42" t="n">
         <v>74</v>
       </c>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -3584,7 +3546,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3608,7 +3570,6 @@
       <c r="G43" t="n">
         <v>142</v>
       </c>
-      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -3641,7 +3602,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3665,7 +3626,6 @@
       <c r="G44" t="n">
         <v>177</v>
       </c>
-      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -3698,7 +3658,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3722,7 +3682,6 @@
       <c r="G45" t="n">
         <v>179</v>
       </c>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -3755,7 +3714,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3779,7 +3738,6 @@
       <c r="G46" t="n">
         <v>177</v>
       </c>
-      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -3812,7 +3770,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3836,7 +3794,6 @@
       <c r="G47" t="n">
         <v>74</v>
       </c>
-      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -3869,7 +3826,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3893,7 +3850,6 @@
       <c r="G48" t="n">
         <v>177</v>
       </c>
-      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -3926,7 +3882,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3950,7 +3906,6 @@
       <c r="G49" t="n">
         <v>142</v>
       </c>
-      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -3983,7 +3938,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -4007,7 +3962,6 @@
       <c r="G50" t="n">
         <v>74</v>
       </c>
-      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -4040,7 +3994,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -4064,7 +4018,6 @@
       <c r="G51" t="n">
         <v>149</v>
       </c>
-      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -4097,7 +4050,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4158,7 +4111,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4182,7 +4135,6 @@
       <c r="G53" t="n">
         <v>74</v>
       </c>
-      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -4215,7 +4167,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4239,7 +4191,6 @@
       <c r="G54" t="n">
         <v>142</v>
       </c>
-      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -4272,7 +4223,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4296,7 +4247,6 @@
       <c r="G55" t="n">
         <v>177</v>
       </c>
-      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -4329,7 +4279,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4353,7 +4303,6 @@
       <c r="G56" t="n">
         <v>74</v>
       </c>
-      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -4386,7 +4335,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4410,7 +4359,6 @@
       <c r="G57" t="n">
         <v>142</v>
       </c>
-      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -4443,7 +4391,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4467,7 +4415,6 @@
       <c r="G58" t="n">
         <v>177</v>
       </c>
-      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -4500,7 +4447,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4524,7 +4471,6 @@
       <c r="G59" t="n">
         <v>149</v>
       </c>
-      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -4557,7 +4503,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4618,7 +4564,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4642,7 +4588,6 @@
       <c r="G61" t="n">
         <v>139</v>
       </c>
-      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -4675,7 +4620,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4699,7 +4644,6 @@
       <c r="G62" t="n">
         <v>127</v>
       </c>
-      <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -4732,7 +4676,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4756,7 +4700,6 @@
       <c r="G63" t="n">
         <v>139</v>
       </c>
-      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -4789,7 +4732,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4813,7 +4756,6 @@
       <c r="G64" t="n">
         <v>138</v>
       </c>
-      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -4846,7 +4788,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4870,7 +4812,6 @@
       <c r="G65" t="n">
         <v>77</v>
       </c>
-      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -4903,7 +4844,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4927,7 +4868,6 @@
       <c r="G66" t="n">
         <v>77</v>
       </c>
-      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -4960,7 +4900,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4984,7 +4924,6 @@
       <c r="G67" t="n">
         <v>138</v>
       </c>
-      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -5017,7 +4956,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -5041,7 +4980,6 @@
       <c r="G68" t="n">
         <v>139</v>
       </c>
-      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -5074,7 +5012,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -5098,7 +5036,6 @@
       <c r="G69" t="n">
         <v>77</v>
       </c>
-      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -5131,7 +5068,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -5155,7 +5092,6 @@
       <c r="G70" t="n">
         <v>138</v>
       </c>
-      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -5188,7 +5124,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -5212,7 +5148,6 @@
       <c r="G71" t="n">
         <v>139</v>
       </c>
-      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -5245,7 +5180,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -5269,7 +5204,6 @@
       <c r="G72" t="n">
         <v>172</v>
       </c>
-      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -5302,7 +5236,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -5326,7 +5260,6 @@
       <c r="G73" t="n">
         <v>169</v>
       </c>
-      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -5359,7 +5292,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -5383,7 +5316,6 @@
       <c r="G74" t="n">
         <v>185</v>
       </c>
-      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -5416,7 +5348,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5440,7 +5372,6 @@
       <c r="G75" t="n">
         <v>185</v>
       </c>
-      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -5473,7 +5404,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5534,7 +5465,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5619,7 +5550,6 @@
       <c r="G78" t="n">
         <v>574</v>
       </c>
-      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -5676,7 +5606,6 @@
       <c r="G79" t="n">
         <v>313</v>
       </c>
-      <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -5733,7 +5662,6 @@
       <c r="G80" t="n">
         <v>372</v>
       </c>
-      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -5790,7 +5718,6 @@
       <c r="G81" t="n">
         <v>313</v>
       </c>
-      <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -5847,7 +5774,6 @@
       <c r="G82" t="n">
         <v>313</v>
       </c>
-      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -5904,7 +5830,6 @@
       <c r="G83" t="n">
         <v>212</v>
       </c>
-      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -5961,7 +5886,6 @@
       <c r="G84" t="n">
         <v>244</v>
       </c>
-      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -6018,7 +5942,6 @@
       <c r="G85" t="n">
         <v>244</v>
       </c>
-      <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -6075,7 +5998,6 @@
       <c r="G86" t="n">
         <v>372</v>
       </c>
-      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -6132,7 +6054,6 @@
       <c r="G87" t="n">
         <v>190</v>
       </c>
-      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -6165,7 +6086,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -6250,7 +6171,6 @@
       <c r="G89" t="n">
         <v>190</v>
       </c>
-      <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -6307,7 +6227,6 @@
       <c r="G90" t="n">
         <v>190</v>
       </c>
-      <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -6364,7 +6283,6 @@
       <c r="G91" t="n">
         <v>190</v>
       </c>
-      <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -6421,7 +6339,6 @@
       <c r="G92" t="n">
         <v>190</v>
       </c>
-      <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -6478,7 +6395,6 @@
       <c r="G93" t="n">
         <v>190</v>
       </c>
-      <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -6535,7 +6451,6 @@
       <c r="G94" t="n">
         <v>190</v>
       </c>
-      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -6568,7 +6483,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6592,7 +6507,6 @@
       <c r="G95" t="n">
         <v>192</v>
       </c>
-      <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -6625,7 +6539,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6649,7 +6563,6 @@
       <c r="G96" t="n">
         <v>241</v>
       </c>
-      <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -6682,7 +6595,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -6706,7 +6619,6 @@
       <c r="G97" t="n">
         <v>208</v>
       </c>
-      <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -6739,7 +6651,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6763,7 +6675,6 @@
       <c r="G98" t="n">
         <v>125</v>
       </c>
-      <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -6796,7 +6707,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6820,7 +6731,6 @@
       <c r="G99" t="n">
         <v>82</v>
       </c>
-      <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -6853,7 +6763,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6877,7 +6787,6 @@
       <c r="G100" t="n">
         <v>175</v>
       </c>
-      <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -6910,7 +6819,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -6934,7 +6843,6 @@
       <c r="G101" t="n">
         <v>82</v>
       </c>
-      <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -6967,7 +6875,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -6991,7 +6899,6 @@
       <c r="G102" t="n">
         <v>243</v>
       </c>
-      <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -7024,7 +6931,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -7048,7 +6955,6 @@
       <c r="G103" t="n">
         <v>131</v>
       </c>
-      <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -7081,7 +6987,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -7105,7 +7011,6 @@
       <c r="G104" t="n">
         <v>131</v>
       </c>
-      <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -7138,7 +7043,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -7162,7 +7067,6 @@
       <c r="G105" t="n">
         <v>131</v>
       </c>
-      <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -7195,7 +7099,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -7219,7 +7123,6 @@
       <c r="G106" t="n">
         <v>247</v>
       </c>
-      <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -7252,7 +7155,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -7276,7 +7179,6 @@
       <c r="G107" t="n">
         <v>175</v>
       </c>
-      <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -7309,7 +7211,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -7333,7 +7235,6 @@
       <c r="G108" t="n">
         <v>175</v>
       </c>
-      <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -7366,7 +7267,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -7390,7 +7291,6 @@
       <c r="G109" t="n">
         <v>83</v>
       </c>
-      <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -7423,7 +7323,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -7484,7 +7384,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -7508,7 +7408,6 @@
       <c r="G111" t="n">
         <v>186</v>
       </c>
-      <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -7541,7 +7440,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -7565,7 +7464,6 @@
       <c r="G112" t="n">
         <v>175</v>
       </c>
-      <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -7598,7 +7496,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -7622,7 +7520,6 @@
       <c r="G113" t="n">
         <v>82</v>
       </c>
-      <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -7655,7 +7552,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -7679,7 +7576,6 @@
       <c r="G114" t="n">
         <v>175</v>
       </c>
-      <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -7712,7 +7608,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -7736,7 +7632,6 @@
       <c r="G115" t="n">
         <v>175</v>
       </c>
-      <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -7769,7 +7664,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -7793,7 +7688,6 @@
       <c r="G116" t="n">
         <v>130</v>
       </c>
-      <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -7826,7 +7720,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -7850,7 +7744,6 @@
       <c r="G117" t="n">
         <v>82</v>
       </c>
-      <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -7883,7 +7776,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -7907,7 +7800,6 @@
       <c r="G118" t="n">
         <v>175</v>
       </c>
-      <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -7940,7 +7832,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -7964,7 +7856,6 @@
       <c r="G119" t="n">
         <v>175</v>
       </c>
-      <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -7997,7 +7888,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -8021,7 +7912,6 @@
       <c r="G120" t="n">
         <v>82</v>
       </c>
-      <c r="H120" t="inlineStr"/>
       <c r="I120" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -8054,7 +7944,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -8078,7 +7968,6 @@
       <c r="G121" t="n">
         <v>175</v>
       </c>
-      <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -8111,7 +8000,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -8172,7 +8061,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -8196,7 +8085,6 @@
       <c r="G123" t="n">
         <v>186</v>
       </c>
-      <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -8229,7 +8117,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -8253,7 +8141,6 @@
       <c r="G124" t="n">
         <v>86</v>
       </c>
-      <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -8286,7 +8173,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -8310,7 +8197,6 @@
       <c r="G125" t="n">
         <v>186</v>
       </c>
-      <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -8343,7 +8229,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -8367,7 +8253,6 @@
       <c r="G126" t="n">
         <v>86</v>
       </c>
-      <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -8400,7 +8285,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -8424,7 +8309,6 @@
       <c r="G127" t="n">
         <v>186</v>
       </c>
-      <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -8457,7 +8341,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -8481,7 +8365,6 @@
       <c r="G128" t="n">
         <v>185</v>
       </c>
-      <c r="H128" t="inlineStr"/>
       <c r="I128" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -8514,7 +8397,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -8538,7 +8421,6 @@
       <c r="G129" t="n">
         <v>185</v>
       </c>
-      <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -8571,7 +8453,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -8595,7 +8477,6 @@
       <c r="G130" t="n">
         <v>185</v>
       </c>
-      <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -8628,7 +8509,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -8652,7 +8533,6 @@
       <c r="G131" t="n">
         <v>175</v>
       </c>
-      <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -8685,7 +8565,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -8709,7 +8589,6 @@
       <c r="G132" t="n">
         <v>125</v>
       </c>
-      <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -8742,7 +8621,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -8766,7 +8645,6 @@
       <c r="G133" t="n">
         <v>185</v>
       </c>
-      <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -8799,7 +8677,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -8860,7 +8738,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -8921,7 +8799,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -8945,7 +8823,6 @@
       <c r="G136" t="n">
         <v>83</v>
       </c>
-      <c r="H136" t="inlineStr"/>
       <c r="I136" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -8978,7 +8855,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -9002,7 +8879,6 @@
       <c r="G137" t="n">
         <v>148</v>
       </c>
-      <c r="H137" t="inlineStr"/>
       <c r="I137" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -9035,7 +8911,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -9059,7 +8935,6 @@
       <c r="G138" t="n">
         <v>190</v>
       </c>
-      <c r="H138" t="inlineStr"/>
       <c r="I138" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -9092,7 +8967,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -9116,7 +8991,6 @@
       <c r="G139" t="n">
         <v>148</v>
       </c>
-      <c r="H139" t="inlineStr"/>
       <c r="I139" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -9149,7 +9023,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -9173,7 +9047,6 @@
       <c r="G140" t="n">
         <v>83</v>
       </c>
-      <c r="H140" t="inlineStr"/>
       <c r="I140" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -9206,7 +9079,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -9230,7 +9103,6 @@
       <c r="G141" t="n">
         <v>208</v>
       </c>
-      <c r="H141" t="inlineStr"/>
       <c r="I141" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -9263,7 +9135,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -9287,7 +9159,6 @@
       <c r="G142" t="n">
         <v>241</v>
       </c>
-      <c r="H142" t="inlineStr"/>
       <c r="I142" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>

--- a/data/availability/projects/marakez/crescent-walk.xlsx
+++ b/data/availability/projects/marakez/crescent-walk.xlsx
@@ -554,7 +554,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -604,7 +604,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -704,7 +704,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -754,7 +754,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2757,7 +2757,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3434,7 +3434,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3546,7 +3546,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3658,7 +3658,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3714,7 +3714,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4167,7 +4167,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4279,7 +4279,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4447,7 +4447,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4620,7 +4620,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4676,7 +4676,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4900,7 +4900,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -5012,7 +5012,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -5236,7 +5236,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -5292,7 +5292,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -6086,7 +6086,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -6483,7 +6483,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6539,7 +6539,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6595,7 +6595,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6707,7 +6707,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6763,7 +6763,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -6875,7 +6875,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -6931,7 +6931,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -6987,7 +6987,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -7099,7 +7099,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -7155,7 +7155,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -7267,7 +7267,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -7323,7 +7323,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -7384,7 +7384,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -7440,7 +7440,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -7496,7 +7496,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -7552,7 +7552,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -7608,7 +7608,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -7664,7 +7664,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -7720,7 +7720,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -7832,7 +7832,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -7888,7 +7888,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -7944,7 +7944,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -8000,7 +8000,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -8117,7 +8117,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -8173,7 +8173,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -8229,7 +8229,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -8285,7 +8285,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -8341,7 +8341,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -8397,7 +8397,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -8453,7 +8453,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -8509,7 +8509,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -8565,7 +8565,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -8621,7 +8621,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -8677,7 +8677,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -8738,7 +8738,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -8799,7 +8799,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -8855,7 +8855,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -8911,7 +8911,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -8967,7 +8967,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -9023,7 +9023,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -9079,7 +9079,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -9135,7 +9135,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
